--- a/system_development/Moultrie/v0.3.1/BOM-v0.3.xlsx
+++ b/system_development/Moultrie/v0.3.1/BOM-v0.3.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mk103\Documents\GitHub\flowthrough-water-quality-monitoring-system\system_development\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\github\flowthrough-water-quality-monitoring-system\system_development\Moultrie\v0.3.1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1ACCD291-A7B6-43B8-8282-284D3F8D52D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3874B28-A2CA-483E-94E5-BE6FD2D245AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{FDAE7DA4-9528-4FC7-A320-70DA50473DCE}"/>
+    <workbookView xWindow="28680" yWindow="-150" windowWidth="29040" windowHeight="15720" xr2:uid="{FDAE7DA4-9528-4FC7-A320-70DA50473DCE}"/>
   </bookViews>
   <sheets>
     <sheet name="bill_of_materials" sheetId="1" r:id="rId1"/>
@@ -173,15 +173,6 @@
     <t>Multipurpose 6061 Aluminum Sheet, 1/8" Thick, 12" x 12"</t>
   </si>
   <si>
-    <t>HDPE Sheet: 0.25 in Thick, 24 in x 24 in, Opaque, Off-White, 4,600 psi Tensile Strength</t>
-  </si>
-  <si>
-    <t>HPDE Sheet</t>
-  </si>
-  <si>
-    <t>https://www.grainger.com/product/HDPE-Sheet-0-25-in-Thick-1ZAL8</t>
-  </si>
-  <si>
     <t>Relay Module</t>
   </si>
   <si>
@@ -189,6 +180,15 @@
   </si>
   <si>
     <t>https://www.ebay.com/itm/166286100101?chn=ps&amp;_trkparms=ispr%3D1&amp;amdata=enc%3A1AOsTJtXlRhetE-2aOOWbuQ28&amp;norover=1&amp;mkrid=711-173151-913341-5&amp;mkcid=2&amp;mkscid=101&amp;itemid=166286100101&amp;targetid=2321110923541&amp;device=c&amp;mktype=pla&amp;googleloc=9010433&amp;poi=&amp;campaignid=21400684010&amp;mkgroupid=173029508068&amp;rlsatarget=pla-2321110923541&amp;abcId=9448486&amp;merchantid=101645423&amp;gad_source=1&amp;gad_campaignid=21400684010&amp;gbraid=0AAAAAD_QDh9jbBqHDR9n1PvmvLpKOq0ju&amp;gclid=CjwKCAjw857RBhAgEiwAI-1yKL9q29fCTuM_gBzzlJIO6D3D1VhA_jDtgUe760kKVIEhhQraJM75choCOgsQAvD_BwE</t>
+  </si>
+  <si>
+    <t>HDPE Sheet: 0.25 in Thick, 12 in x 24 in, Opaque, Black, 4,600 psi Tensile Strength, 1.94 ft-lb/in</t>
+  </si>
+  <si>
+    <t>plastic shelf material</t>
+  </si>
+  <si>
+    <t>https://www.grainger.com/product/HDPE-Sheet-0-25-in-Thick-1ZAW2</t>
   </si>
 </sst>
 </file>
@@ -897,31 +897,31 @@
     </row>
     <row r="13" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="C13" s="2">
         <v>2</v>
       </c>
       <c r="D13" s="6">
-        <v>31.19</v>
+        <v>12.24</v>
       </c>
       <c r="E13" s="6">
         <f t="shared" si="0"/>
-        <v>62.38</v>
+        <v>24.48</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
     </row>
     <row r="14" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="C14" s="2">
         <v>5</v>
@@ -934,7 +934,7 @@
         <v>6.1</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="G14" s="3"/>
       <c r="H14" s="3"/>
@@ -1002,7 +1002,7 @@
       </c>
       <c r="E21" s="8">
         <f>SUM(E2:E20)</f>
-        <v>578.93000000000006</v>
+        <v>541.03</v>
       </c>
     </row>
     <row r="22" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -1169,7 +1169,7 @@
       </c>
       <c r="E42" s="6">
         <f>SUM(E2:E41)</f>
-        <v>1157.8600000000001</v>
+        <v>1082.06</v>
       </c>
     </row>
   </sheetData>
@@ -1184,7 +1184,7 @@
     <hyperlink ref="F8" r:id="rId8" xr:uid="{7BAB4E45-A6E5-B54E-B4E7-980D3A49764F}"/>
     <hyperlink ref="F10" r:id="rId9" xr:uid="{29553635-2A91-4048-BD3A-AA2B63BC1E10}"/>
     <hyperlink ref="F9" r:id="rId10" xr:uid="{AF43F826-6010-5F46-85BE-E2B9217CA3AF}"/>
-    <hyperlink ref="F13" r:id="rId11" xr:uid="{A878F3CB-05D4-4A32-A97B-B6F814AE55A2}"/>
+    <hyperlink ref="F13" r:id="rId11" xr:uid="{769B87DA-C404-435B-A0B2-0353F64D15F8}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId12"/>
